--- a/output/graficos_dimensiones/comunal_d_depmen_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:05</t>
+    <t xml:space="preserve">2026-09-10 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:18</t>
+    <t xml:space="preserve">2026-09-12 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:29</t>
+    <t xml:space="preserve">2026-09-23 23:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1120,8 +1120,12 @@
       <c r="C34" s="2" t="n">
         <v>6204</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="D34" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>24.34</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>
